--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/CchbPrdBaseInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/CchbPrdBaseInfo001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
   <si>
     <t>产品基础信息</t>
   </si>
@@ -148,6 +148,286 @@
   </si>
   <si>
     <t>以财产权信托名义开展的资金信托标识</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每天开放</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每周开放一次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每两周开放一次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">04 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每月开放一次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每季度开放一次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">06 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每半年开放一次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">07 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每年开放一次</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">99 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他规律开放周期</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>申赎皆可</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">02 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仅可申购无限制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仅可赎回无限制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">04 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仅可申购有限制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">05 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仅可赎回有限制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">99 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>其他</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -160,7 +440,7 @@
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +450,12 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -183,22 +469,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,7 +510,42 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,17 +559,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -250,53 +592,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
@@ -304,16 +599,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,12 +613,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -343,19 +628,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,13 +742,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -385,61 +778,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,73 +802,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -537,26 +822,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -576,17 +863,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,187 +919,185 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1145,184 +1448,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AM2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:AM3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col min="3" max="3" width="14.3333333333333" customWidth="1"/>
     <col min="4" max="4" width="13.2222222222222" customWidth="1"/>
+    <col min="5" max="8" width="9" style="2"/>
+    <col min="10" max="10" width="9.55555555555556" customWidth="1"/>
+    <col min="20" max="20" width="9" style="2"/>
+    <col min="32" max="32" width="9" style="2"/>
+    <col min="39" max="39" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="3" t="s">
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3" t="s">
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="1" t="s">
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1" t="s">
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="4"/>
     </row>
     <row r="2" spans="1:39">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AE2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AF2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AI2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AK2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AL2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AM2" s="6" t="s">
         <v>37</v>
       </c>
+    </row>
+    <row r="3" spans="5:5">
+      <c r="E3" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1333,6 +1644,41 @@
     <mergeCell ref="AG1:AH1"/>
     <mergeCell ref="AI1:AM1"/>
   </mergeCells>
+  <dataValidations count="11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA1 AA3:AA1048576">
+      <formula1>"01 发行成功,02 发行失败,03 确认发行"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 W3:W1048576">
+      <formula1>Sheet2!$A$10:$A$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 U1 AG1 AH1 AL1 L3:L1048576 U3:U1048576 AG3:AG1048576 AH3:AH1048576 AL3:AL1048576">
+      <formula1>"01 是,02 否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 I3:I1048576">
+      <formula1>"01 集合管理,02 单独管理"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 O3:O1048576">
+      <formula1>"01 有规律开放,02 无规律开放"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1 P3:P1048576">
+      <formula1>Sheet2!$A$1:$A$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE1 AE3:AE1048576">
+      <formula1>"01 ACT/366,02 ACT/360,03 ACT/365,04 ACT/ACT,05 30/360   "</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1 Y3:Y1048576">
+      <formula1>"C 周期型产品,M 货币型产品,N 净值型产品,R 利率型产品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AI3:AI1048576">
+      <formula1>"01 主动管理,02 被动管理"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1 AJ3:AJ1048576">
+      <formula1>"01 收益权转让,99 其他特定目的载体"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK1 AK3:AK1048576">
+      <formula1>"1 单位,2 个人,3 个人及单位"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1342,9 +1688,80 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/CchbPrdBaseInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/CchbPrdBaseInfo001.xlsx
@@ -16,27 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
-  <si>
-    <t>产品基础信息</t>
-  </si>
-  <si>
-    <t>发行登记</t>
-  </si>
-  <si>
-    <t>募集总量登记</t>
-  </si>
-  <si>
-    <t>终止登记</t>
-  </si>
-  <si>
-    <t>非保本月报/G06</t>
-  </si>
-  <si>
-    <t>人行报送信息</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>产品代码</t>
+  </si>
+  <si>
+    <t>行内标识码</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -435,12 +420,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,7 +448,136 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -477,142 +591,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FF080808"/>
       <name val="宋体"/>
@@ -628,49 +606,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,133 +774,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -824,10 +802,56 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -849,39 +873,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -898,24 +889,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -927,10 +905,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -939,137 +917,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1079,12 +1057,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1093,12 +1065,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1448,234 +1414,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AM3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <dimension ref="A1:AN2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
-    <col min="3" max="3" width="14.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.2222222222222" customWidth="1"/>
-    <col min="5" max="8" width="9" style="2"/>
-    <col min="10" max="10" width="9.55555555555556" customWidth="1"/>
-    <col min="20" max="20" width="9" style="2"/>
-    <col min="32" max="32" width="9" style="2"/>
-    <col min="39" max="39" width="9" style="2"/>
+    <col min="4" max="4" width="14.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="6" max="9" width="9" style="2"/>
+    <col min="11" max="11" width="9.55555555555556" customWidth="1"/>
+    <col min="21" max="21" width="9" style="2"/>
+    <col min="33" max="33" width="9" style="2"/>
+    <col min="40" max="40" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:40">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF1" s="9"/>
-      <c r="AG1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH1" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="AI1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ1" s="3"/>
-      <c r="AK1" s="3"/>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="4" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:39">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI2" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="AJ2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AK2" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AM2" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="5:5">
-      <c r="E3" s="7"/>
+    <row r="2" spans="6:6">
+      <c r="F2" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L1:AB1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AI1:AM1"/>
-  </mergeCells>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA1 AA3:AA1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>"01 发行成功,02 发行失败,03 确认发行"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 W3:W1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
+      <formula1>"01 有规律开放,02 无规律开放"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"01 集合管理,02 单独管理"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576 V2:V1048576 AH2:AH1048576 AI2:AI1048576 AM2:AM1048576">
+      <formula1>"01 是,02 否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576">
+      <formula1>Sheet2!$A$1:$A$8</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576">
+      <formula1>"A/360 A/360,A/365 A/365"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
       <formula1>Sheet2!$A$10:$A$15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 U1 AG1 AH1 AL1 L3:L1048576 U3:U1048576 AG3:AG1048576 AH3:AH1048576 AL3:AL1048576">
-      <formula1>"01 是,02 否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 I3:I1048576">
-      <formula1>"01 集合管理,02 单独管理"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 O3:O1048576">
-      <formula1>"01 有规律开放,02 无规律开放"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P1 P3:P1048576">
-      <formula1>Sheet2!$A$1:$A$8</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE1 AE3:AE1048576">
-      <formula1>"01 ACT/366,02 ACT/360,03 ACT/365,04 ACT/ACT,05 30/360   "</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1 Y3:Y1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>"C 周期型产品,M 货币型产品,N 净值型产品,R 利率型产品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AI3:AI1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ1048576">
       <formula1>"01 主动管理,02 被动管理"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1 AJ3:AJ1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK2:AK1048576">
       <formula1>"01 收益权转让,99 其他特定目的载体"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK1 AK3:AK1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AL1048576">
       <formula1>"1 单位,2 个人,3 个人及单位"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1693,72 +1601,72 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/CchbPrdBaseInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/CchbPrdBaseInfo001.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\产品3.0.6单信披\tams\tams-svreport-parent\tams-svreport-chb\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>产品代码</t>
   </si>
@@ -140,7 +145,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">01 </t>
     </r>
@@ -149,6 +154,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>每天开放</t>
@@ -160,7 +166,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">02 </t>
     </r>
@@ -169,6 +175,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>每周开放一次</t>
@@ -180,7 +187,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">03 </t>
     </r>
@@ -189,6 +196,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>每两周开放一次</t>
@@ -200,7 +208,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">04 </t>
     </r>
@@ -209,6 +217,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>每月开放一次</t>
@@ -220,7 +229,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">05 </t>
     </r>
@@ -229,6 +238,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>每季度开放一次</t>
@@ -240,7 +250,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">06 </t>
     </r>
@@ -249,6 +259,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>每半年开放一次</t>
@@ -260,7 +271,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">07 </t>
     </r>
@@ -269,6 +280,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>每年开放一次</t>
@@ -280,7 +292,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">99 </t>
     </r>
@@ -289,6 +301,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>其他规律开放周期</t>
@@ -300,7 +313,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">01 </t>
     </r>
@@ -309,6 +322,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>申赎皆可</t>
@@ -320,7 +334,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">02 </t>
     </r>
@@ -329,6 +343,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>仅可申购无限制</t>
@@ -340,7 +355,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">03 </t>
     </r>
@@ -349,6 +364,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>仅可赎回无限制</t>
@@ -360,7 +376,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">04 </t>
     </r>
@@ -369,6 +385,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>仅可申购有限制</t>
@@ -380,7 +397,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">05 </t>
     </r>
@@ -389,6 +406,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>仅可赎回有限制</t>
@@ -400,7 +418,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="Consolas"/>
-        <charset val="134"/>
+        <family val="3"/>
       </rPr>
       <t xml:space="preserve">99 </t>
     </r>
@@ -409,6 +427,7 @@
         <sz val="10.5"/>
         <color rgb="FF080808"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>其他</t>
@@ -418,14 +437,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,361 +450,40 @@
       <sz val="10.5"/>
       <color rgb="FF080808"/>
       <name val="Consolas"/>
-      <charset val="134"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF080808"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -799,251 +491,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1067,61 +517,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1408,25 +814,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:AN2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AM2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="14.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="14.375" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
     <col min="6" max="9" width="9" style="2"/>
-    <col min="11" max="11" width="9.55555555555556" customWidth="1"/>
+    <col min="11" max="11" width="9.5" customWidth="1"/>
     <col min="21" max="21" width="9" style="2"/>
     <col min="33" max="33" width="9" style="2"/>
-    <col min="40" max="40" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1544,15 +949,13 @@
       <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="6:6">
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.15">
       <c r="F2" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="11">
+  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>"01 发行成功,02 发行失败,03 确认发行"</formula1>
     </dataValidation>
@@ -1565,14 +968,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576 V2:V1048576 AH2:AH1048576 AI2:AI1048576 AM2:AM1048576">
       <formula1>"01 是,02 否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q1048576">
-      <formula1>Sheet2!$A$1:$A$8</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF1048576">
       <formula1>"A/360 A/360,A/365 A/365"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X1048576">
-      <formula1>Sheet2!$A$10:$A$15</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z1048576">
       <formula1>"C 周期型产品,M 货币型产品,N 净值型产品,R 利率型产品"</formula1>
@@ -1589,101 +986,116 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$1:$A$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>Q2:Q1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$10:$A$15</xm:f>
+          </x14:formula1>
+          <xm:sqref>X2:X1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>